--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1234-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1234-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F069BA4A-0A44-4ED5-ABA6-0E4F1D017DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F291D07-1F8F-443A-A731-B8904D433AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9C52E693-0DCD-4017-A1F4-98A42D436ECF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{60C7AFBA-9528-4BA3-B945-BDB65674941E}"/>
   </bookViews>
   <sheets>
     <sheet name="1234-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1532,27 +1532,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B62E9A9-27A6-491C-B682-3D55686A43C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED20FD9-5244-4FAC-BFA2-5328B2073FA0}">
   <dimension ref="A1:X60"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +1585,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1622,7 +1621,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1674,7 +1673,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1742,7 +1741,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1814,7 +1813,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1886,7 +1885,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2030,7 +2029,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2174,7 +2173,7 @@
         <v>6.15</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>2018</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2017</v>
       </c>
@@ -2318,7 +2317,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2016</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2015</v>
       </c>
@@ -2462,7 +2461,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2014</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2013</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2012</v>
       </c>
@@ -2678,7 +2677,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2011</v>
       </c>
@@ -2750,7 +2749,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2010</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2009</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2008</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2007</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2006</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2005</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2004</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2003</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2002</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2001</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2000</v>
       </c>
@@ -3542,7 +3541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>1999</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>7.81</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>1998</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1997</v>
       </c>
@@ -3758,7 +3757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42"/>
       <c r="B33" s="43"/>
       <c r="C33" s="19" t="s">
@@ -3786,7 +3785,7 @@
       <c r="W33" s="49"/>
       <c r="X33" s="45"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1996</v>
       </c>
@@ -3858,7 +3857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>1995</v>
       </c>
@@ -3930,7 +3929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1994</v>
       </c>
@@ -4002,7 +4001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1993</v>
       </c>
@@ -4074,7 +4073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1992</v>
       </c>
@@ -4146,7 +4145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>1991</v>
       </c>
@@ -4218,7 +4217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>1990</v>
       </c>
@@ -4290,7 +4289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1989</v>
       </c>
@@ -4362,7 +4361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>1986</v>
       </c>
@@ -4434,7 +4433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>1985</v>
       </c>
@@ -4506,7 +4505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1984</v>
       </c>
@@ -4578,7 +4577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1983</v>
       </c>
@@ -4650,7 +4649,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>1982</v>
       </c>
@@ -4722,7 +4721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1981</v>
       </c>
@@ -4794,7 +4793,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>1980</v>
       </c>
@@ -4866,7 +4865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1979</v>
       </c>
@@ -4938,7 +4937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="36">
         <v>1978</v>
       </c>
@@ -5010,7 +5009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1977</v>
       </c>
@@ -5082,7 +5081,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="36">
         <v>1976</v>
       </c>
@@ -5154,7 +5153,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>1975</v>
       </c>
@@ -5226,7 +5225,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="36">
         <v>1974</v>
       </c>
@@ -5298,7 +5297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>1973</v>
       </c>
@@ -5370,7 +5369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="36">
         <v>1972</v>
       </c>
@@ -5442,7 +5441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38">
         <v>1971</v>
       </c>
@@ -5514,7 +5513,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="36">
         <v>1970</v>
       </c>
@@ -5586,7 +5585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="38">
         <v>1969</v>
       </c>
@@ -5658,7 +5657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="36" t="s">
         <v>57</v>
       </c>
